--- a/redmine-logger/backend/user_data/lumiqshubh23/timelog.xlsx
+++ b/redmine-logger/backend/user_data/lumiqshubh23/timelog.xlsx
@@ -397,20 +397,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:E97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>date</v>
+        <v>Date</v>
       </c>
       <c r="B1" t="str">
-        <v>issue_id</v>
+        <v>CR-DM-PDM ID</v>
       </c>
       <c r="C1" t="str">
-        <v>hours</v>
+        <v>Effort</v>
       </c>
       <c r="D1" t="str">
-        <v>comments</v>
+        <v>Type</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Activity Description</v>
       </c>
     </row>
     <row r="2">
@@ -421,9 +424,12 @@
         <v>158484</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E2" t="str">
         <v>Merge branch 'insure/develop' into infinityInsure2.0/uat</v>
       </c>
     </row>
@@ -435,9 +441,12 @@
         <v>158484</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E3" t="str">
         <v>fix: sync package-lock with package.json</v>
       </c>
     </row>
@@ -449,9 +458,12 @@
         <v>158484</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E4" t="str">
         <v>Merge remote-tracking branch 'origin/insure/develop' into infinityInsure2.0/uat</v>
       </c>
     </row>
@@ -466,21 +478,27 @@
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>Merge branch 'insure/develop' into infinityInsure2.0/uat</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B6">
         <v>158484</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Merge branch 'insure/develop' into infinityInsure2.0/uat</v>
       </c>
     </row>
     <row r="7">
@@ -491,9 +509,12 @@
         <v>158484</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E7" t="str">
         <v>package json fix</v>
       </c>
     </row>
@@ -505,9 +526,12 @@
         <v>158484</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E8" t="str">
         <v>sync package.json issue</v>
       </c>
     </row>
@@ -519,24 +543,30 @@
         <v>158484</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>Merge branch 'insure/develop' into infinityInsure2.0/uat</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="B10">
         <v>158484</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Merge branch 'insure/develop' into infinityInsure2.0/uat</v>
       </c>
     </row>
     <row r="11">
@@ -547,9 +577,12 @@
         <v>158484</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E11" t="str">
         <v>rider premium mapping</v>
       </c>
     </row>
@@ -561,9 +594,12 @@
         <v>158484</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E12" t="str">
         <v>BI called with rider</v>
       </c>
     </row>
@@ -575,15 +611,18 @@
         <v>158484</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="str">
-        <v>Merge branch 'insure/develop' into insure/develop-secureInvest</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B14">
         <v>158484</v>
@@ -592,7 +631,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Merge branch 'insure/develop' into insure/develop-secureInvest</v>
       </c>
     </row>
     <row r="15">
@@ -606,6 +648,9 @@
         <v>4</v>
       </c>
       <c r="D15" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E15" t="str">
         <v>controller fix</v>
       </c>
     </row>
@@ -617,9 +662,12 @@
         <v>158484</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E16" t="str">
         <v>Merge branch 'insure/develop-secureInvest' into insure/develop</v>
       </c>
     </row>
@@ -631,9 +679,12 @@
         <v>158484</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E17" t="str">
         <v>Merge remote-tracking branch 'origin/insure/develop' into uat-common-backend-1</v>
       </c>
     </row>
@@ -648,6 +699,9 @@
         <v>1</v>
       </c>
       <c r="D18" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E18" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
@@ -662,6 +716,9 @@
         <v>3</v>
       </c>
       <c r="D19" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E19" t="str">
         <v>Merge remote-tracking branch 'origin/insure/develop' into uat-common-backend-1</v>
       </c>
     </row>
@@ -673,9 +730,12 @@
         <v>158484</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E20" t="str">
         <v>Merge branch 'insure2.0/secureInvest' into insure/develop</v>
       </c>
     </row>
@@ -687,9 +747,12 @@
         <v>158484</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E21" t="str">
         <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure2.0/secureInvest</v>
       </c>
     </row>
@@ -704,6 +767,9 @@
         <v>1</v>
       </c>
       <c r="D22" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E22" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
@@ -715,9 +781,12 @@
         <v>158484</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E23" t="str">
         <v>rider</v>
       </c>
     </row>
@@ -729,9 +798,12 @@
         <v>158484</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E24" t="str">
         <v>Merge branch 'insure/develop' of https://github.com/lumiqai/isnp-backend-v2 into insure/develop-secureInvest</v>
       </c>
     </row>
@@ -746,6 +818,9 @@
         <v>4</v>
       </c>
       <c r="D25" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E25" t="str">
         <v>secure invest fm</v>
       </c>
     </row>
@@ -760,21 +835,27 @@
         <v>1</v>
       </c>
       <c r="D26" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Merge remote-tracking branch 'origin/insure/develop' into insure/develop-secureInvest</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-08</v>
       </c>
       <c r="B27">
         <v>158484</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="str">
-        <v>Merge remote-tracking branch 'origin/insure/develop' into insure/develop-secureInvest</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="28">
@@ -785,9 +866,12 @@
         <v>158484</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E28" t="str">
         <v>generate bi api integartion and fallback of fund alloction</v>
       </c>
     </row>
@@ -802,6 +886,9 @@
         <v>3</v>
       </c>
       <c r="D29" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E29" t="str">
         <v>Merge branch 'insure/develop-secureInvest' into uat-common-backend-1</v>
       </c>
     </row>
@@ -813,9 +900,12 @@
         <v>158484</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E30" t="str">
         <v>Merge branch 'insure/develop' into insure2.0/secureInvest</v>
       </c>
     </row>
@@ -830,6 +920,9 @@
         <v>1</v>
       </c>
       <c r="D31" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E31" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
@@ -844,6 +937,9 @@
         <v>3</v>
       </c>
       <c r="D32" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E32" t="str">
         <v>add</v>
       </c>
     </row>
@@ -855,9 +951,12 @@
         <v>158484</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E33" t="str">
         <v>add</v>
       </c>
     </row>
@@ -869,9 +968,12 @@
         <v>158484</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E34" t="str">
         <v>secureInvest-riderAdded</v>
       </c>
     </row>
@@ -886,21 +988,27 @@
         <v>1</v>
       </c>
       <c r="D35" t="str">
-        <v>Merge remote-tracking branch 'origin/mvp-2'</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-13</v>
       </c>
       <c r="B36">
         <v>158484</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Merge remote-tracking branch 'origin/mvp-2'</v>
       </c>
     </row>
     <row r="37">
@@ -911,9 +1019,12 @@
         <v>158484</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E37" t="str">
         <v>mvp-2</v>
       </c>
     </row>
@@ -925,9 +1036,12 @@
         <v>158484</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E38" t="str">
         <v>redmine connection feature added</v>
       </c>
     </row>
@@ -939,24 +1053,30 @@
         <v>158484</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="str">
-        <v>prod ready</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B40">
         <v>158484</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E40" t="str">
+        <v>prod ready</v>
       </c>
     </row>
     <row r="41">
@@ -967,9 +1087,12 @@
         <v>158484</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E41" t="str">
         <v>deployment setup</v>
       </c>
     </row>
@@ -981,9 +1104,12 @@
         <v>158484</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E42" t="str">
         <v>MVP-1</v>
       </c>
     </row>
@@ -998,6 +1124,9 @@
         <v>1</v>
       </c>
       <c r="D43" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E43" t="str">
         <v>working fine</v>
       </c>
     </row>
@@ -1012,6 +1141,9 @@
         <v>1</v>
       </c>
       <c r="D44" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E44" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
@@ -1023,9 +1155,12 @@
         <v>158484</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E45" t="str">
         <v>ui fix</v>
       </c>
     </row>
@@ -1040,6 +1175,9 @@
         <v>1</v>
       </c>
       <c r="D46" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E46" t="str">
         <v>apu sheet creation</v>
       </c>
     </row>
@@ -1051,9 +1189,12 @@
         <v>158484</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E47" t="str">
         <v>commit fetch done</v>
       </c>
     </row>
@@ -1068,6 +1209,9 @@
         <v>2</v>
       </c>
       <c r="D48" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E48" t="str">
         <v>commit fetch api inprocess</v>
       </c>
     </row>
@@ -1079,9 +1223,12 @@
         <v>158484</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E49" t="str">
         <v>inital structure ready</v>
       </c>
     </row>
@@ -1096,6 +1243,9 @@
         <v>1</v>
       </c>
       <c r="D50" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E50" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
@@ -1107,9 +1257,12 @@
         <v>158484</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E51" t="str">
         <v>Merge branch 'ISNP2.0-viewDoc' into insure/develop</v>
       </c>
     </row>
@@ -1121,9 +1274,12 @@
         <v>158484</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E52" t="str">
         <v>view doc</v>
       </c>
     </row>
@@ -1135,9 +1291,12 @@
         <v>158484</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E53" t="str">
         <v>Merge branch 'insure/develop' into uat-common-backend-1</v>
       </c>
     </row>
@@ -1152,6 +1311,9 @@
         <v>2</v>
       </c>
       <c r="D54" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E54" t="str">
         <v>create excel and logtime both</v>
       </c>
     </row>
@@ -1166,6 +1328,9 @@
         <v>1</v>
       </c>
       <c r="D55" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E55" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
@@ -1177,9 +1342,12 @@
         <v>158484</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E56" t="str">
         <v>redmine logtime in a issue</v>
       </c>
     </row>
@@ -1191,9 +1359,12 @@
         <v>158484</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E57" t="str">
         <v>first commit</v>
       </c>
     </row>
@@ -1208,6 +1379,9 @@
         <v>1</v>
       </c>
       <c r="D58" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E58" t="str">
         <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
@@ -1219,38 +1393,47 @@
         <v>158484</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="str">
-        <v>ComponentCmpTagToggleSwitch fix</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-20</v>
       </c>
       <c r="B60">
         <v>158484</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E60" t="str">
+        <v>ComponentCmpTagToggleSwitch fix</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-20</v>
       </c>
       <c r="B61">
         <v>158484</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
     <row r="62">
@@ -1261,9 +1444,12 @@
         <v>158484</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E62" t="str">
         <v>staff discount key fix</v>
       </c>
     </row>
@@ -1278,49 +1464,61 @@
         <v>1</v>
       </c>
       <c r="D63" t="str">
-        <v>changemedicalquestionvalue</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="B64">
         <v>158484</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="str">
-        <v>change in fm and rm</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E64" t="str">
+        <v>changemedicalquestionvalue</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="B65">
         <v>158484</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="str">
-        <v>Merge branch 'pennydropIntegration' into insure/develop</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E65" t="str">
+        <v>change in fm and rm</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="B66">
         <v>158484</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Merge branch 'pennydropIntegration' into insure/develop</v>
       </c>
     </row>
     <row r="67">
@@ -1331,9 +1529,12 @@
         <v>158484</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E67" t="str">
         <v>penny drop api integration</v>
       </c>
     </row>
@@ -1348,26 +1549,32 @@
         <v>1</v>
       </c>
       <c r="D68" t="str">
-        <v>Merge branch 'insure-api-wrapper' of https://github.com/lumiqai/isnp-backend-v2 into insure-api-wrapper</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-22</v>
       </c>
       <c r="B69">
         <v>158484</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="str">
-        <v>retailduplicateApplicationNumber</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Merge branch 'insure-api-wrapper' of https://github.com/lumiqai/isnp-backend-v2 into insure-api-wrapper</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-22</v>
       </c>
       <c r="B70">
         <v>158484</v>
@@ -1376,7 +1583,10 @@
         <v>1</v>
       </c>
       <c r="D70" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E70" t="str">
+        <v>retailduplicateApplicationNumber</v>
       </c>
     </row>
     <row r="71">
@@ -1387,9 +1597,12 @@
         <v>158484</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E71" t="str">
         <v>application number exist api</v>
       </c>
     </row>
@@ -1404,6 +1617,9 @@
         <v>2</v>
       </c>
       <c r="D72" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E72" t="str">
         <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
       </c>
     </row>
@@ -1418,6 +1634,9 @@
         <v>1</v>
       </c>
       <c r="D73" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E73" t="str">
         <v>rename route for insure2</v>
       </c>
     </row>
@@ -1432,6 +1651,9 @@
         <v>1</v>
       </c>
       <c r="D74" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E74" t="str">
         <v>make pan wrapper generic</v>
       </c>
     </row>
@@ -1446,12 +1668,15 @@
         <v>1</v>
       </c>
       <c r="D75" t="str">
-        <v>generic wrapper</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="B76">
         <v>158484</v>
@@ -1460,7 +1685,10 @@
         <v>1</v>
       </c>
       <c r="D76" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E76" t="str">
+        <v>generic wrapper</v>
       </c>
     </row>
     <row r="77">
@@ -1471,9 +1699,12 @@
         <v>158484</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E77" t="str">
         <v>new routes for ISNP2.0</v>
       </c>
     </row>
@@ -1485,9 +1716,12 @@
         <v>158484</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E78" t="str">
         <v>upload proceed now bg color fix</v>
       </c>
     </row>
@@ -1499,9 +1733,12 @@
         <v>158484</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E79" t="str">
         <v>upload proceed now bg color fix</v>
       </c>
     </row>
@@ -1513,24 +1750,30 @@
         <v>158484</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="str">
-        <v>for EQUITAS no setIsLaMinor check</v>
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="B81">
         <v>158484</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="str">
-        <v>Daily Scrum Call</v>
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E81" t="str">
+        <v>for EQUITAS no setIsLaMinor check</v>
       </c>
     </row>
     <row r="82">
@@ -1541,9 +1784,12 @@
         <v>158484</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E82" t="str">
         <v>Merge branch 'CR-36689-backend' into uat-common-backend-1</v>
       </c>
     </row>
@@ -1558,6 +1804,9 @@
         <v>1</v>
       </c>
       <c r="D83" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E83" t="str">
         <v>proposal form photo</v>
       </c>
     </row>
@@ -1569,9 +1818,12 @@
         <v>158484</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D84" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E84" t="str">
         <v>Merge remote-tracking branch 'origin/CR-36689-sgp' into smartGuaranteedPension-frontend</v>
       </c>
     </row>
@@ -1586,6 +1838,9 @@
         <v>1</v>
       </c>
       <c r="D85" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E85" t="str">
         <v>SGP dynamic heading restore</v>
       </c>
     </row>
@@ -1600,12 +1855,202 @@
         <v>1</v>
       </c>
       <c r="D86" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B87">
+        <v>158484</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Merge remote-tracking branch 'origin/CR-36689-backend' into uat-common-backend-1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B88">
+        <v>158484</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E88" t="str">
+        <v>LA=&gt;PR in proposal form</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B89">
+        <v>158484</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Merge branch 'CR-36689-cpf' into secureInvestPlan-frontend</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B90">
+        <v>158484</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Merge branch 'CR-36689-ytp' into youngTermPlan-frontend</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B91">
+        <v>158484</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Merge branch 'smartGuaranteedPension-frontend' of https://github.com/lumiqai/ISNP into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B92">
+        <v>158484</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B93">
+        <v>158484</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B94">
+        <v>158484</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Merge branch 'CR-36689-sgp' of https://github.com/lumiqai/ISNP into CR-36689-sgp</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B95">
+        <v>158484</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E95" t="str">
+        <v>dynamic heading added for nomiee</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B96">
+        <v>158484</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Merge branch 'CR-36689-sgp' into smartGuaranteedPension-frontend</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B97">
+        <v>158484</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Daily SCRUM</v>
+      </c>
+      <c r="E97" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/redmine-logger/backend/user_data/lumiqshubh23/timelog.xlsx
+++ b/redmine-logger/backend/user_data/lumiqshubh23/timelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,7 +418,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B2">
         <v>158484</v>
@@ -427,49 +427,49 @@
         <v>4</v>
       </c>
       <c r="D2" t="str">
-        <v>Development &amp; Configuration</v>
+        <v>Meeting</v>
       </c>
       <c r="E2" t="str">
-        <v>General Work</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B3">
         <v>158484</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>Meeting</v>
+        <v>Development &amp; Configuration</v>
       </c>
       <c r="E3" t="str">
-        <v>Daily Scrum Call</v>
+        <v>DM-22984 deathcover factor in igf</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B4">
         <v>158484</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="str">
-        <v>Daily SCRUM</v>
+        <v>Development &amp; Configuration</v>
       </c>
       <c r="E4" t="str">
-        <v>Daily Scrum Call</v>
+        <v>DM-23043</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-02</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B5">
         <v>158484</v>
@@ -478,66 +478,66 @@
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>Integration/Merge</v>
+        <v>Daily SCRUM</v>
       </c>
       <c r="E5" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-02</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B6">
         <v>158484</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="str">
-        <v>Meeting</v>
+        <v>Development &amp; Configuration</v>
       </c>
       <c r="E6" t="str">
-        <v>Daily Scrum Call</v>
+        <v>secureInvest  continue button issue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-02</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B7">
         <v>158484</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="str">
-        <v>Integration/Merge</v>
+        <v>Meeting</v>
       </c>
       <c r="E7" t="str">
-        <v>Merge branch 'pennydropIntegration' into insure/develop</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-02</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B8">
         <v>158484</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>Feature</v>
+        <v>Development &amp; Configuration</v>
       </c>
       <c r="E8" t="str">
-        <v>penny drop api integration</v>
+        <v>DM-23087 The “Are you opting for Staff Discount?” option should be placed after the “Annual Income” field.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-02</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B9">
         <v>158484</v>
@@ -546,236 +546,15 @@
         <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>Meeting</v>
+        <v>Daily SCRUM</v>
       </c>
       <c r="E9" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="B10">
-        <v>158484</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Integration/Merge</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="B11">
-        <v>158484</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Daily SCRUM</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>2026-06-03</v>
-      </c>
-      <c r="B12">
-        <v>158484</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Bug Fix</v>
-      </c>
-      <c r="E12" t="str">
-        <v>ComponentCmpTagToggleSwitch fix</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2026-06-03</v>
-      </c>
-      <c r="B13">
-        <v>158484</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Integration/Merge</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Merge branch 'insure/develop' of https://github.com/lumiqai/ISNP into insure/develop</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2026-06-03</v>
-      </c>
-      <c r="B14">
-        <v>158484</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Bug Fix</v>
-      </c>
-      <c r="E14" t="str">
-        <v>staff discount key fix</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>2026-06-03</v>
-      </c>
-      <c r="B15">
-        <v>158484</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Daily SCRUM</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="B16">
-        <v>158484</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Refactor</v>
-      </c>
-      <c r="E16" t="str">
-        <v>changemedicalquestionvalue</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="B17">
-        <v>158484</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Meeting</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="B18">
-        <v>158484</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Feature</v>
-      </c>
-      <c r="E18" t="str">
-        <v>inital structure ready</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="B19">
-        <v>158484</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Daily SCRUM</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>2026-06-05</v>
-      </c>
-      <c r="B20">
-        <v>158484</v>
-      </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Meeting</v>
-      </c>
-      <c r="E20" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>2026-06-05</v>
-      </c>
-      <c r="B21">
-        <v>158484</v>
-      </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Integration/Merge</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Merge branch 'insure/develop' into insure2.0/secureInvest</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-06-05</v>
-      </c>
-      <c r="B22">
-        <v>158484</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Daily SCRUM</v>
-      </c>
-      <c r="E22" t="str">
-        <v>Daily Scrum Call</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/redmine-logger/backend/user_data/lumiqshubh23/timelog.xlsx
+++ b/redmine-logger/backend/user_data/lumiqshubh23/timelog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,7 +458,7 @@
         <v>158484</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="str">
         <v>Development &amp; Configuration</v>
@@ -478,27 +478,27 @@
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>Daily SCRUM</v>
+        <v>Development &amp; Configuration</v>
       </c>
       <c r="E5" t="str">
-        <v>Daily Scrum Call</v>
+        <v>secureInvest  continue button issue</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B6">
         <v>158484</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="str">
-        <v>Development &amp; Configuration</v>
+        <v>Daily SCRUM</v>
       </c>
       <c r="E6" t="str">
-        <v>secureInvest  continue button issue</v>
+        <v>Daily Scrum Call</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         <v>158484</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="str">
         <v>Meeting</v>
@@ -526,7 +526,7 @@
         <v>158484</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="str">
         <v>Development &amp; Configuration</v>
@@ -546,15 +546,32 @@
         <v>1</v>
       </c>
       <c r="D9" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DM-23089 "Are you opting for Staff Discount?"option is currently displayed in the Life Assured (LA) Details section</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="B10">
+        <v>158484</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="str">
         <v>Daily SCRUM</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E10" t="str">
         <v>Daily Scrum Call</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
   </ignoredErrors>
 </worksheet>
 </file>